--- a/www/flightdata/xlsx/eoss-352.xlsx
+++ b/www/flightdata/xlsx/eoss-352.xlsx
@@ -2994,7 +2994,7 @@
         <v>22054.11</v>
       </c>
       <c r="I2">
-        <v>548</v>
+        <v>362</v>
       </c>
       <c r="J2" t="s">
         <v>43</v>
